--- a/pseudodata/1111.xlsx
+++ b/pseudodata/1111.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,24 +536,24 @@
         <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009196027673716398</v>
+        <v>0.001816671765467053</v>
       </c>
       <c r="M2" t="n">
-        <v>5.30860538661124e-05</v>
+        <v>0.001022932081695123</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0004598013836858199</v>
+        <v>9.083358827335264e-05</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -590,24 +590,24 @@
         <v>0.1</v>
       </c>
       <c r="I3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009939859798804082</v>
+        <v>0.001515316008085403</v>
       </c>
       <c r="M3" t="n">
-        <v>7.155908433810674e-05</v>
+        <v>0.001041781600269328</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0004969929899402042</v>
+        <v>7.576580040427017e-05</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -644,24 +644,24 @@
         <v>0.1</v>
       </c>
       <c r="I4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00944106727760239</v>
+        <v>0.001076637533965002</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0001008716826647291</v>
+        <v>0.001139650159357878</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0004720533638801195</v>
+        <v>5.38318766982501e-05</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -698,24 +698,24 @@
         <v>0.1</v>
       </c>
       <c r="I5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007947484269321783</v>
+        <v>0.0005387278976794317</v>
       </c>
       <c r="M5" t="n">
-        <v>0.000143787624139224</v>
+        <v>0.00132618219133069</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0003973742134660892</v>
+        <v>2.693639488397159e-05</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -752,24 +752,24 @@
         <v>0.1</v>
       </c>
       <c r="I6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005793144688670067</v>
+        <v>-8.511408608476192e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0002048265683601953</v>
+        <v>0.001623456616056035</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0002896572344335034</v>
+        <v>-4.255704304238096e-06</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -806,24 +806,24 @@
         <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002948678190530666</v>
+        <v>-0.0007915284287954843</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002840458150573266</v>
+        <v>0.002064650861855071</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001474339095265333</v>
+        <v>-3.957642143977421e-05</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -860,24 +860,24 @@
         <v>0.1</v>
       </c>
       <c r="I8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0005906556030279097</v>
+        <v>-0.001576963034672648</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0003745373962914396</v>
+        <v>0.002693270760596351</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.953278015139549e-05</v>
+        <v>-7.88481517336324e-05</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -908,30 +908,30 @@
         <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="H9" t="n">
         <v>0.1</v>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0005148809411207802</v>
+        <v>-0.002432181521915321</v>
       </c>
       <c r="M9" t="n">
-        <v>7.507501735032484e-05</v>
+        <v>0.00356363761472211</v>
       </c>
       <c r="N9" t="n">
-        <v>2.574404705603901e-05</v>
+        <v>-0.000121609076095766</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -962,30 +962,30 @@
         <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
         <v>0.1</v>
       </c>
       <c r="I10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0005531434465741898</v>
+        <v>-0.003338209024956007</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0001011998275819507</v>
+        <v>0.004742488548542998</v>
       </c>
       <c r="N10" t="n">
-        <v>2.765717232870949e-05</v>
+        <v>-0.0001669104512478003</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1016,30 +1016,30 @@
         <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="H11" t="n">
         <v>0.1</v>
       </c>
       <c r="I11" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0004207708466985396</v>
+        <v>-0.004258739360061448</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0001426541016838549</v>
+        <v>0.006303187854451726</v>
       </c>
       <c r="N11" t="n">
-        <v>2.103854233492698e-05</v>
+        <v>-0.0002129369680030724</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1070,30 +1070,30 @@
         <v>0.5</v>
       </c>
       <c r="G12" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
         <v>0.1</v>
       </c>
       <c r="I12" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L12" t="n">
-        <v>0.000195066865504116</v>
+        <v>-0.005130849836868265</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0002033464081590957</v>
+        <v>0.008294552812714786</v>
       </c>
       <c r="N12" t="n">
-        <v>9.7533432752058e-06</v>
+        <v>-0.0002565424918434132</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1124,30 +1124,30 @@
         <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H13" t="n">
         <v>0.1</v>
       </c>
       <c r="I13" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L13" t="n">
-        <v>-8.367750651561678e-05</v>
+        <v>-0.005872186965562814</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0002896685109093281</v>
+        <v>0.010686681428485</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.183875325780839e-06</v>
+        <v>-0.0002936093482781407</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1178,30 +1178,30 @@
         <v>0.5</v>
       </c>
       <c r="G14" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
         <v>0.1</v>
       </c>
       <c r="I14" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.000383060575185077</v>
+        <v>-0.006426443536978035</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0004017014439893911</v>
+        <v>0.01337363739534133</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.915302875925385e-05</v>
+        <v>-0.0003213221768489018</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1232,30 +1232,30 @@
         <v>0.5</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="H15" t="n">
         <v>0.1</v>
       </c>
       <c r="I15" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.00064476097071267</v>
+        <v>-0.006812502555695149</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0005296758654512603</v>
+        <v>0.01632171425154224</v>
       </c>
       <c r="N15" t="n">
-        <v>-3.223804853563351e-05</v>
+        <v>-0.0003406251277847575</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1286,30 +1286,30 @@
         <v>0.5</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
         <v>0.1</v>
       </c>
       <c r="I16" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L16" t="n">
-        <v>4.785766209016035e-05</v>
+        <v>-0.007096156213429725</v>
       </c>
       <c r="M16" t="n">
-        <v>7.507501735032484e-05</v>
+        <v>0.01971482798240609</v>
       </c>
       <c r="N16" t="n">
-        <v>2.392883104508018e-06</v>
+        <v>-0.0003548078106714863</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1340,30 +1340,30 @@
         <v>0.5</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="H17" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0001612530544044314</v>
+        <v>-0.007316705311159306</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0001011998275819507</v>
+        <v>0.02385105939384964</v>
       </c>
       <c r="N17" t="n">
-        <v>8.06265272022157e-06</v>
+        <v>-0.0003658352655579653</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1394,30 +1394,30 @@
         <v>0.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H18" t="n">
         <v>0.1</v>
       </c>
       <c r="I18" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0002137284935795153</v>
+        <v>-0.007459172529753877</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0001426541016838549</v>
+        <v>0.02881061135062982</v>
       </c>
       <c r="N18" t="n">
-        <v>1.068642467897576e-05</v>
+        <v>-0.0003729586264876939</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1425,600 +1425,6 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>100</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>50</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>100</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.0002059830310863229</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.0002033464081590957</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1.029915155431615e-05</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>100</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>50</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>100</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.0001542527260848044</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.0002896685109093281</v>
-      </c>
-      <c r="N20" t="n">
-        <v>7.712636304240218e-06</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>100</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>50</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>100</v>
-      </c>
-      <c r="L21" t="n">
-        <v>7.896618600072113e-05</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.0004017014439893911</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.948309300036057e-06</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>100</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>50</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>100</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.524234491050779e-06</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.0005296758654512603</v>
-      </c>
-      <c r="N22" t="n">
-        <v>7.621172455253894e-08</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="n">
-        <v>100</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>50</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L23" t="n">
-        <v>-1.483271534042054e-05</v>
-      </c>
-      <c r="M23" t="n">
-        <v>7.507501735032484e-05</v>
-      </c>
-      <c r="N23" t="n">
-        <v>-7.416357670210269e-07</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>100</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>50</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>100</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-4.292808605376939e-06</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.0001011998275819507</v>
-      </c>
-      <c r="N24" t="n">
-        <v>-2.14640430268847e-07</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>100</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>50</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>100</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2.229327991201954e-05</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.0001426541016838549</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.114663995600977e-06</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>100</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>50</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>100</v>
-      </c>
-      <c r="L26" t="n">
-        <v>6.284798340396882e-05</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.0002033464081590957</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.142399170198441e-06</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>100</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G27" t="n">
-        <v>4</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>50</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>100</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.0001100010840951743</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.0002896685109093281</v>
-      </c>
-      <c r="N27" t="n">
-        <v>5.500054204758716e-06</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>100</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I28" t="n">
-        <v>50</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>100</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.0001512758747573619</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.0004017014439893911</v>
-      </c>
-      <c r="N28" t="n">
-        <v>7.563793737868094e-06</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B29" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
-        <v>100</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G29" t="n">
-        <v>5</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I29" t="n">
-        <v>50</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>100</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.0001865556963516443</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.0005296758654512603</v>
-      </c>
-      <c r="N29" t="n">
-        <v>9.327784817582217e-06</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P29" t="n">
         <v>1</v>
       </c>
     </row>
